--- a/VerveStacks_MYS_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_MYS_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6073AF-EE7E-46EB-8496-7A75BF921902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{027DE038-8EF8-4B52-813D-658F97B91AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{A550C9B0-1C6C-4FBC-AA46-F049CD6B5F46}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{3525F691-758A-4BEF-BD91-25E6A883DF63}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1843,7 +1843,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{531959DB-5AA6-4AD3-9B07-4A58CC34AF08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2640CAA-4854-4166-AF94-426C303326BC}">
   <dimension ref="B3:L196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
